--- a/packages-generated/GB Accounts Company 2026-03-31 (Mar26) Excel 2007/Vatreturns.xlsx
+++ b/packages-generated/GB Accounts Company 2026-03-31 (Mar26) Excel 2007/Vatreturns.xlsx
@@ -40,7 +40,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">VATQtr4!$A$1:$I$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">VATQtr5!$A$1:$I$31</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
